--- a/CALIDAD_AGUA/database/Base_Sintetica_Calidad_Agua_Rio_Chili.xlsx
+++ b/CALIDAD_AGUA/database/Base_Sintetica_Calidad_Agua_Rio_Chili.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GITHUB\DASHBOARDS\CALIDAD DE AGUA\database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brv_1\Documents\Programacion\PORTAFOLIOS\DASHBOARDS2\CALIDAD_AGUA\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F969D84-E87D-429A-9461-64C4EE5E9801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEE5060-5117-4B7B-83B0-95BC0982C6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -971,9 +971,6 @@
       <c r="P8" s="2">
         <v>0.77</v>
       </c>
-      <c r="Q8" s="2">
-        <v>141.80000000000001</v>
-      </c>
       <c r="R8" s="2">
         <v>0.13700000000000001</v>
       </c>
@@ -1080,9 +1077,6 @@
       <c r="K10" s="2">
         <v>381.2</v>
       </c>
-      <c r="L10" s="2">
-        <v>12.2</v>
-      </c>
       <c r="M10" s="2">
         <v>37.6</v>
       </c>
@@ -1320,7 +1314,7 @@
         <v>17.3</v>
       </c>
       <c r="I14" s="2">
-        <v>7.59</v>
+        <v>7.73</v>
       </c>
       <c r="J14" s="2">
         <v>6.74</v>
@@ -1827,9 +1821,6 @@
       <c r="L22" s="2">
         <v>12.8</v>
       </c>
-      <c r="M22" s="2">
-        <v>32.299999999999997</v>
-      </c>
       <c r="N22" s="2">
         <v>6.24</v>
       </c>
@@ -2645,9 +2636,6 @@
       <c r="P35" s="2">
         <v>0.47</v>
       </c>
-      <c r="Q35" s="2">
-        <v>127.6</v>
-      </c>
       <c r="R35" s="2">
         <v>0.104</v>
       </c>
@@ -3928,9 +3916,6 @@
       </c>
       <c r="J56" s="2">
         <v>6.28</v>
-      </c>
-      <c r="K56" s="2">
-        <v>755</v>
       </c>
       <c r="L56" s="2">
         <v>11</v>
